--- a/artfynd/A 56010-2025 artfynd.xlsx
+++ b/artfynd/A 56010-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130007612</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>130112232</v>
       </c>
       <c r="B3" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>130111964</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>130111956</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56010-2025 artfynd.xlsx
+++ b/artfynd/A 56010-2025 artfynd.xlsx
@@ -792,38 +792,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130112232</v>
+        <v>130111964</v>
       </c>
       <c r="B3" t="n">
-        <v>57016</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471174</v>
+        <v>471194</v>
       </c>
       <c r="R3" t="n">
-        <v>6539106</v>
+        <v>6539124</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På sten</t>
+          <t>Färska födohack på klen granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130111964</v>
+        <v>130111956</v>
       </c>
       <c r="B4" t="n">
         <v>57823</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471194</v>
+        <v>471196</v>
       </c>
       <c r="R4" t="n">
-        <v>6539124</v>
+        <v>6539105</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska födohack på klen granlåga</t>
+          <t>Färska födohack på granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130111956</v>
+        <v>130324022</v>
       </c>
       <c r="B5" t="n">
         <v>57823</v>
@@ -1057,7 +1057,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471196</v>
+        <v>471220</v>
       </c>
       <c r="R5" t="n">
-        <v>6539105</v>
+        <v>6539107</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1096,27 +1096,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska födohack på granlåga</t>
+          <t>Äldre födohack vid basen av högstubbe.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130324022</v>
+        <v>130323961</v>
       </c>
       <c r="B6" t="n">
         <v>57823</v>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471220</v>
+        <v>471230</v>
       </c>
       <c r="R6" t="n">
-        <v>6539107</v>
+        <v>6539096</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av högstubbe.</t>
+          <t>Äldre födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,50 +1260,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130323961</v>
+        <v>130323834</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>91695</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471230</v>
+        <v>471220</v>
       </c>
       <c r="R7" t="n">
-        <v>6539096</v>
+        <v>6539090</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1335,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1340,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre födohack på låga av tall.</t>
+          <t>På lutande död gran. Lutar mot stor sten.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130323834</v>
+        <v>130324138</v>
       </c>
       <c r="B8" t="n">
-        <v>91692</v>
+        <v>5197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,34 +1383,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471220</v>
+        <v>471184</v>
       </c>
       <c r="R8" t="n">
-        <v>6539090</v>
+        <v>6539088</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På lutande död gran. Lutar mot stor sten.</t>
+          <t>Äldre gnag och kläckhål vid basen av död stående gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130324271</v>
+        <v>130112232</v>
       </c>
       <c r="B9" t="n">
         <v>57016</v>
@@ -1518,16 +1518,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471181</v>
+        <v>471174</v>
       </c>
       <c r="R9" t="n">
-        <v>6538991</v>
+        <v>6539106</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1554,27 +1559,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fjäder från höna</t>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,22 +1594,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130324138</v>
+        <v>130324271</v>
       </c>
       <c r="B10" t="n">
-        <v>5197</v>
+        <v>57016</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,39 +1617,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Boramossen, Boramossen, Vg</t>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471184</v>
+        <v>471181</v>
       </c>
       <c r="R10" t="n">
-        <v>6539088</v>
+        <v>6538991</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre gnag och kläckhål vid basen av död stående gran.</t>
+          <t>Fjäder från höna</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,12 +1706,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 56010-2025 artfynd.xlsx
+++ b/artfynd/A 56010-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>130111964</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>130111956</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>130324022</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>130323961</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>130323834</v>
       </c>
       <c r="B7" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>130112232</v>
       </c>
       <c r="B9" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>130324271</v>
       </c>
       <c r="B10" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 56010-2025 artfynd.xlsx
+++ b/artfynd/A 56010-2025 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>130323834</v>
       </c>
       <c r="B7" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56010-2025 artfynd.xlsx
+++ b/artfynd/A 56010-2025 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>130323834</v>
       </c>
       <c r="B7" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56010-2025 artfynd.xlsx
+++ b/artfynd/A 56010-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>130324022</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>130323961</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>130323834</v>
       </c>
       <c r="B7" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>130112232</v>
       </c>
       <c r="B9" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>130324271</v>
       </c>
       <c r="B10" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 56010-2025 artfynd.xlsx
+++ b/artfynd/A 56010-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>130324022</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>130323961</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>130323834</v>
       </c>
       <c r="B7" t="n">
-        <v>91725</v>
+        <v>91737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>130112232</v>
       </c>
       <c r="B9" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>130324271</v>
       </c>
       <c r="B10" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 56010-2025 artfynd.xlsx
+++ b/artfynd/A 56010-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>130324022</v>
       </c>
       <c r="B5" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>130323961</v>
       </c>
       <c r="B6" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>130323834</v>
       </c>
       <c r="B7" t="n">
-        <v>91737</v>
+        <v>91738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>130112232</v>
       </c>
       <c r="B9" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>130324271</v>
       </c>
       <c r="B10" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 56010-2025 artfynd.xlsx
+++ b/artfynd/A 56010-2025 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>130324022</v>
       </c>
       <c r="B5" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>130323961</v>
       </c>
       <c r="B6" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>130323834</v>
       </c>
       <c r="B7" t="n">
-        <v>91738</v>
+        <v>91739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56010-2025 artfynd.xlsx
+++ b/artfynd/A 56010-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130007612</v>
+        <v>130323834</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471170</v>
+        <v>471220</v>
       </c>
       <c r="R2" t="n">
-        <v>6539084</v>
+        <v>6539090</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -745,27 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska och äldre tretåhack med savflöde på hela tallen. Sveaskog har snitslat rödgul snitsel på trädet.</t>
+          <t>På lutande död gran. Lutar mot stor sten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,14 +787,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130111964</v>
+        <v>130111956</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471194</v>
+        <v>471196</v>
       </c>
       <c r="R3" t="n">
-        <v>6539124</v>
+        <v>6539105</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska födohack på klen granlåga</t>
+          <t>Färska födohack på granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,14 +904,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130111956</v>
+        <v>130111964</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471196</v>
+        <v>471194</v>
       </c>
       <c r="R4" t="n">
-        <v>6539105</v>
+        <v>6539124</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska födohack på granlåga</t>
+          <t>Färska födohack på klen granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,14 +1021,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130324022</v>
+        <v>130323961</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471220</v>
+        <v>471230</v>
       </c>
       <c r="R5" t="n">
-        <v>6539107</v>
+        <v>6539096</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen av högstubbe.</t>
+          <t>Äldre födohack på låga av tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,14 +1138,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130323961</v>
+        <v>130324022</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1183,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471230</v>
+        <v>471220</v>
       </c>
       <c r="R6" t="n">
-        <v>6539096</v>
+        <v>6539107</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1218,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre födohack på låga av tall.</t>
+          <t>Äldre födohack vid basen av högstubbe.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,45 +1255,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130323834</v>
+        <v>130007612</v>
       </c>
       <c r="B7" t="n">
-        <v>91739</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471220</v>
+        <v>471170</v>
       </c>
       <c r="R7" t="n">
-        <v>6539090</v>
+        <v>6539084</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1325,27 +1325,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På lutande död gran. Lutar mot stor sten.</t>
+          <t>Färska och äldre tretåhack med savflöde på hela tallen. Sveaskog har snitslat rödgul snitsel på trädet.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,27 +1372,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130324138</v>
+        <v>130007648</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1403,7 +1403,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471184</v>
+        <v>471153</v>
       </c>
       <c r="R8" t="n">
-        <v>6539088</v>
+        <v>6539097</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1442,27 +1442,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre gnag och kläckhål vid basen av död stående gran.</t>
+          <t>Äldre ringhack på död avbruten tall där barken börjat ramla av. 3 m fr tall med färska ringhack.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,38 +1489,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130112232</v>
+        <v>130007713</v>
       </c>
       <c r="B9" t="n">
-        <v>57073</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471174</v>
+        <v>471152</v>
       </c>
       <c r="R9" t="n">
-        <v>6539106</v>
+        <v>6539084</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1559,27 +1559,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På sten</t>
+          <t>Äldre ringhack på död tall där barken börjat lossa. Ca 10 m fr tall med färska spår.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130324271</v>
+        <v>130112232</v>
       </c>
       <c r="B10" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,16 +1635,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
+          <t>Boramossen, Boramossen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471181</v>
+        <v>471174</v>
       </c>
       <c r="R10" t="n">
-        <v>6538991</v>
+        <v>6539106</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1671,27 +1676,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fjäder från höna</t>
+          <t>På sten</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,15 +1711,244 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130324271</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Åsmossevägen N, Vargaviddernas naturreservat, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>471181</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6538991</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fjäder från höna</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>David Tverling</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>David Tverling</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130324138</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Boramossen, Boramossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>471184</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6539088</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål vid basen av död stående gran.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56010-2025 artfynd.xlsx
+++ b/artfynd/A 56010-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1835,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130324138</v>
+        <v>130323532</v>
       </c>
       <c r="B12" t="n">
-        <v>5199</v>
+        <v>4776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,21 +1846,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471184</v>
+        <v>471193</v>
       </c>
       <c r="R12" t="n">
-        <v>6539088</v>
+        <v>6538984</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre gnag och kläckhål vid basen av död stående gran.</t>
+          <t>Äldre gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,6 +1949,123 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130324138</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Boramossen, Boramossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>471184</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6539088</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre gnag och kläckhål vid basen av död stående gran.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56010-2025 artfynd.xlsx
+++ b/artfynd/A 56010-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130323834</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130111956</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130111964</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130323961</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130324022</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,6 +1399,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130007612</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1486,6 +1521,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130007648</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1603,6 +1643,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130007713</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1720,6 +1765,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130112232</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130324271</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1949,6 +2004,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130323532</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2066,8 +2126,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130324138</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>